--- a/consent_forms/037_patient_education_animation_voiceover_consent_form--consent_forms.xlsx
+++ b/consent_forms/037_patient_education_animation_voiceover_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_recorded_and_stored_for_an_extended_period_of_time</t>
+          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_recorded_and_stored_for_an_extended_period_of</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_used_to_improve_products_or_services_including_pharmacuetical_or_device</t>
+          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_used_to_improve_products_or_services_including</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>informed consent</t>
+          <t>Patient Education Animation Voiceover Consent Form Do You Agree To Provide Your Informed Consent</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>informed consent</t>
+          <t>Patient Education Animation Voiceover Consent Form I Agree To Provide Your Informed Consent</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent</t>
+          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>informed consent</t>
+          <t>Patient Education Animation Voiceover Consent Form I Agree To Provide Your Informed Consent 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>informed consent</t>
+          <t>Patient Education Animation Voiceover Consent Form I Will Provide Y Your Informed Consent</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent</t>
+          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>informed consent</t>
+          <t>Patient Education Animation Voiceover Consent Form I Agree To Provide Your Informed Consent 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>informed consent</t>
+          <t>Patient Education Animation Voiceover Consent Form I Agree To Provide Y Y</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_recorded_and_stored_for_an_extended_period_of_time_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_recorded_and_stored_for_an_extended_period_of_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_recorded_and_stored_for_an_extended_period_of_time_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_recorded_and_stored_for_an_extended_period_of_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_used_to_improve_products_or_services_including_pharmacuetical_or_device_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_used_to_improve_products_or_services_including_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_used_to_improve_products_or_services_including_pharmacuetical_or_device_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_do_you_want_your_voice_used_to_improve_products_or_services_including_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1328,7 +1328,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_choices</t>
+          <t>patient_education_animation_voiceover_consent_form_i_agree_to_provide_your_informed_consent_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
